--- a/cfg/excel/__beans__.xlsx
+++ b/cfg/excel/__beans__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17385" windowHeight="18675"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="230">
   <si>
     <t>##var</t>
   </si>
@@ -313,6 +313,36 @@
     <t>Title("事件id")</t>
   </si>
   <si>
+    <t>Asset</t>
+  </si>
+  <si>
+    <t>AssetType</t>
+  </si>
+  <si>
+    <t>资产类型</t>
+  </si>
+  <si>
+    <t>Title("资产类型")</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>资产id</t>
+  </si>
+  <si>
+    <t>Title("资产id")</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>资产数量</t>
+  </si>
+  <si>
+    <t>Title("资产数量")</t>
+  </si>
+  <si>
     <t>ItemData</t>
   </si>
   <si>
@@ -322,9 +352,6 @@
     <t>物品id</t>
   </si>
   <si>
-    <t>count</t>
-  </si>
-  <si>
     <t>数量</t>
   </si>
   <si>
@@ -668,6 +695,33 @@
   </si>
   <si>
     <t>回血间隔（秒）；首次在一个间隔后触发</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>浜岀淮鍚戦噺</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>涓夌淮鍚戦噺</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>vector4</t>
+  </si>
+  <si>
+    <t>鍥涚淮鍚戦噺</t>
+  </si>
+  <si>
+    <t>w</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P154"/>
+  <dimension ref="A1:166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1877,7 +1931,7 @@
     <col min="12" max="12" width="19.5" style="3" customWidth="1"/>
     <col min="13" max="13" width="10.3833333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="14.3833333333333" style="3" customWidth="1"/>
-    <col min="15" max="15" width="61.75" style="3" customWidth="1"/>
+    <col min="15" max="15" width="61.25" style="3" customWidth="1"/>
     <col min="16" max="16" width="14.25" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
@@ -2410,180 +2464,203 @@
         <v>36</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="O30" s="3" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="2:15">
       <c r="J31" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="20" customHeight="1" spans="2:15">
-      <c r="B32" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" spans="2:15">
+      <c r="O31" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="2:15">
+      <c r="J32" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>98</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
         <v>36</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" spans="2:15">
-      <c r="B34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O34" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="35" ht="20" customHeight="1" spans="2:15">
-      <c r="J35" s="3" t="s">
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="B35" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N35" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:16">
+      <c r="B36" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" spans="2:15">
-      <c r="B36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N36" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="3" t="s">
+      <c r="O36" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="N36" s="3" t="s">
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:16">
+      <c r="B37" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="O36" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="37" s="3" customFormat="1" ht="20" customHeight="1" spans="2:15">
-      <c r="B37" s="3" t="s">
+      <c r="L37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="N37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" s="3" customFormat="1" ht="20" customHeight="1" spans="2:15">
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:16">
       <c r="J38" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N38" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="O38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="O38" s="3" t="s">
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:16">
+      <c r="B39" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="2:15">
-      <c r="B39" s="3" t="s">
+      <c r="E39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1" spans="2:15">
+      <c r="N39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="B40" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>35</v>
@@ -2592,50 +2669,35 @@
         <v>36</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="2:15">
-      <c r="B41" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="J41" s="3" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" spans="2:15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:16">
       <c r="B42" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>35</v>
@@ -2643,25 +2705,13 @@
       <c r="I42" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1" spans="2:15">
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:16">
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>35</v>
@@ -2670,25 +2720,25 @@
         <v>36</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1" spans="2:15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="1:16">
       <c r="B44" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E44" s="3" t="s">
         <v>35</v>
       </c>
@@ -2696,38 +2746,50 @@
         <v>36</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O44" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:16">
+      <c r="B45" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N45" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" ht="20" customHeight="1" spans="2:15">
-      <c r="J45" s="3" t="s">
+      <c r="O45" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1" spans="2:15">
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="1:16">
       <c r="B46" s="3" t="s">
         <v>135</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>35</v>
@@ -2736,76 +2798,64 @@
         <v>36</v>
       </c>
       <c r="J46" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N46" s="3" t="s">
+      <c r="O46" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="O46" s="3" t="s">
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:16">
+      <c r="B47" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="47" ht="20" customHeight="1" spans="2:15">
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N47" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="O47" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1" spans="2:15">
-      <c r="B48" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>36</v>
-      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:16">
       <c r="J48" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="2:15">
       <c r="B49" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>35</v>
@@ -2814,24 +2864,24 @@
         <v>36</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="2:15">
       <c r="B50" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>35</v>
@@ -2840,50 +2890,50 @@
         <v>36</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="2:15">
       <c r="B51" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="L51" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="2:15">
       <c r="B52" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>35</v>
@@ -2892,24 +2942,24 @@
         <v>36</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="2:15">
       <c r="B53" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>35</v>
@@ -2918,50 +2968,50 @@
         <v>36</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="2:15">
       <c r="B54" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O54" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="2:15">
       <c r="B55" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>35</v>
@@ -2970,24 +3020,24 @@
         <v>36</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="2:15">
       <c r="B56" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>35</v>
@@ -2996,50 +3046,50 @@
         <v>36</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="2:15">
       <c r="B57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="2:15">
       <c r="B58" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>35</v>
@@ -3048,24 +3098,24 @@
         <v>36</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="2:15">
       <c r="B59" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>35</v>
@@ -3074,24 +3124,24 @@
         <v>36</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="2:15">
       <c r="B60" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>35</v>
@@ -3100,24 +3150,24 @@
         <v>36</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="2:15">
       <c r="B61" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>35</v>
@@ -3126,24 +3176,24 @@
         <v>36</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="2:15">
       <c r="B62" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>35</v>
@@ -3152,24 +3202,24 @@
         <v>36</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="2:15">
       <c r="B63" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>35</v>
@@ -3178,24 +3228,24 @@
         <v>36</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="2:15">
       <c r="B64" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>35</v>
@@ -3204,24 +3254,24 @@
         <v>36</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:16">
       <c r="B65" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>35</v>
@@ -3230,24 +3280,24 @@
         <v>36</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:16">
       <c r="B66" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>35</v>
@@ -3256,24 +3306,24 @@
         <v>36</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:16">
       <c r="B67" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>35</v>
@@ -3282,24 +3332,24 @@
         <v>36</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:16">
       <c r="B68" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>35</v>
@@ -3308,24 +3358,24 @@
         <v>36</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:16">
       <c r="B69" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>35</v>
@@ -3334,21 +3384,24 @@
         <v>36</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>46</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:16">
       <c r="B70" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>35</v>
@@ -3356,13 +3409,25 @@
       <c r="I70" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="71" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="J70" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:16">
       <c r="B71" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>35</v>
@@ -3371,237 +3436,218 @@
         <v>36</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="72" s="3" customFormat="1" spans="1:16">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="1:16">
       <c r="B72" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="O72" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="73" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:16">
       <c r="B73" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="E73" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
       <c r="B74" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J74" s="3" t="s">
+      <c r="L74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N74" s="3" t="s">
+      <c r="O74" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="O74" s="3" t="s">
+    </row>
+    <row r="75" s="3" customFormat="1" spans="1:16">
+      <c r="B75" s="3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="75" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J75" s="3" t="s">
+      <c r="L75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N75" s="3" t="s">
+      <c r="O75" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="O75" s="3" t="s">
+    </row>
+    <row r="76" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="B76" s="3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="76" ht="20" customHeight="1" spans="1:16">
-      <c r="A76"/>
-      <c r="B76" t="s">
+      <c r="C76" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C76"/>
-      <c r="D76"/>
-      <c r="E76" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76"/>
-      <c r="G76" t="s">
+      <c r="L76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="B77" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H76"/>
-      <c r="I76" t="s">
-        <v>36</v>
-      </c>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76"/>
-      <c r="M76"/>
-      <c r="N76"/>
-      <c r="O76"/>
-      <c r="P76"/>
-    </row>
-    <row r="77" ht="20" customHeight="1" spans="1:16">
-      <c r="A77"/>
-      <c r="B77" t="s">
+      <c r="C77" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C77" t="s">
-        <v>196</v>
-      </c>
-      <c r="D77"/>
-      <c r="E77" t="s">
-        <v>23</v>
-      </c>
-      <c r="F77"/>
-      <c r="G77" t="s">
+      <c r="L77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N77" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H77"/>
-      <c r="I77" t="s">
-        <v>36</v>
-      </c>
-      <c r="J77" t="s">
+      <c r="O77" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="K77"/>
-      <c r="L77" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77"/>
-      <c r="N77" t="s">
+    </row>
+    <row r="78" s="3" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="B78" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="O77"/>
-      <c r="P77"/>
-    </row>
-    <row r="78" ht="20" customHeight="1" spans="1:16">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78" t="s">
+      <c r="C78" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K78"/>
-      <c r="L78" t="s">
-        <v>26</v>
-      </c>
-      <c r="M78"/>
-      <c r="N78" t="s">
+      <c r="L78" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N78" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="O78"/>
-      <c r="P78"/>
+      <c r="O78" s="3" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:16">
       <c r="A79"/>
-      <c r="B79"/>
+      <c r="B79" t="s">
+        <v>205</v>
+      </c>
       <c r="C79"/>
       <c r="D79"/>
-      <c r="E79"/>
+      <c r="E79" t="s">
+        <v>23</v>
+      </c>
       <c r="F79"/>
-      <c r="G79"/>
+      <c r="G79" t="s">
+        <v>206</v>
+      </c>
       <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79" t="s">
-        <v>204</v>
-      </c>
+      <c r="I79" t="s">
+        <v>36</v>
+      </c>
+      <c r="J79"/>
       <c r="K79"/>
-      <c r="L79" t="s">
-        <v>26</v>
-      </c>
+      <c r="L79"/>
       <c r="M79"/>
-      <c r="N79" t="s">
-        <v>205</v>
-      </c>
+      <c r="N79"/>
       <c r="O79"/>
       <c r="P79"/>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:16">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D80"/>
       <c r="E80" t="s">
@@ -3609,22 +3655,22 @@
       </c>
       <c r="F80"/>
       <c r="G80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H80"/>
       <c r="I80" t="s">
         <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K80"/>
       <c r="L80" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M80"/>
       <c r="N80" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O80"/>
       <c r="P80"/>
@@ -3640,7 +3686,7 @@
       <c r="H81"/>
       <c r="I81"/>
       <c r="J81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K81"/>
       <c r="L81" t="s">
@@ -3648,14 +3694,93 @@
       </c>
       <c r="M81"/>
       <c r="N81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O81"/>
       <c r="P81"/>
     </row>
-    <row r="82" ht="20" customHeight="1"/>
-    <row r="83" ht="20" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1" spans="1:16">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82" t="s">
+        <v>213</v>
+      </c>
+      <c r="K82"/>
+      <c r="L82" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82"/>
+      <c r="N82" t="s">
+        <v>214</v>
+      </c>
+      <c r="O82"/>
+      <c r="P82"/>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:16">
+      <c r="A83"/>
+      <c r="B83" t="s">
+        <v>215</v>
+      </c>
+      <c r="C83" t="s">
+        <v>205</v>
+      </c>
+      <c r="D83"/>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83"/>
+      <c r="G83" t="s">
+        <v>216</v>
+      </c>
+      <c r="H83"/>
+      <c r="I83" t="s">
+        <v>36</v>
+      </c>
+      <c r="J83" t="s">
+        <v>217</v>
+      </c>
+      <c r="K83"/>
+      <c r="L83" t="s">
+        <v>46</v>
+      </c>
+      <c r="M83"/>
+      <c r="N83" t="s">
+        <v>218</v>
+      </c>
+      <c r="O83"/>
+      <c r="P83"/>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:16">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84" t="s">
+        <v>219</v>
+      </c>
+      <c r="K84"/>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84"/>
+      <c r="N84" t="s">
+        <v>220</v>
+      </c>
+      <c r="O84"/>
+      <c r="P84"/>
+    </row>
     <row r="85" ht="20" customHeight="1"/>
     <row r="86" ht="20" customHeight="1"/>
     <row r="87" ht="20" customHeight="1"/>
@@ -3726,6 +3851,117 @@
     <row r="152" ht="20" customHeight="1"/>
     <row r="153" ht="20" customHeight="1"/>
     <row r="154" ht="20" customHeight="1"/>
+    <row r="155" ht="20" customHeight="1"/>
+    <row r="156" ht="20" customHeight="1"/>
+    <row r="157" ht="20" customHeight="1"/>
+    <row r="158">
+      <c r="B158" t="s">
+        <v>29</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158" t="s">
+        <v>221</v>
+      </c>
+      <c r="G158" t="s">
+        <v>222</v>
+      </c>
+      <c r="J158" t="s">
+        <v>223</v>
+      </c>
+      <c r="L158" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="J159" t="s">
+        <v>224</v>
+      </c>
+      <c r="L159" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="s">
+        <v>124</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160" t="s">
+        <v>221</v>
+      </c>
+      <c r="G160" t="s">
+        <v>225</v>
+      </c>
+      <c r="J160" t="s">
+        <v>223</v>
+      </c>
+      <c r="L160" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="J161" t="s">
+        <v>224</v>
+      </c>
+      <c r="L161" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="J162" t="s">
+        <v>226</v>
+      </c>
+      <c r="L162" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="s">
+        <v>227</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163" t="s">
+        <v>221</v>
+      </c>
+      <c r="G163" t="s">
+        <v>228</v>
+      </c>
+      <c r="J163" t="s">
+        <v>223</v>
+      </c>
+      <c r="L163" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="J164" t="s">
+        <v>224</v>
+      </c>
+      <c r="L164" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="J165" t="s">
+        <v>226</v>
+      </c>
+      <c r="L165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="J166" t="s">
+        <v>229</v>
+      </c>
+      <c r="L166" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
